--- a/initial_26_Fall_mod.xlsx
+++ b/initial_26_Fall_mod.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weimannd\Documents\VSCode_Local\ELO-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\ELO-main(2)\ELO-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C89C997-4B9E-4831-93A9-A6FE30A9CEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74AE2A0-5280-45FE-9759-9187B1540706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40125" yWindow="6345" windowWidth="16575" windowHeight="12585" xr2:uid="{FB22F9A6-9212-4FA4-9C6C-9674B77F5971}"/>
+    <workbookView xWindow="28455" yWindow="0" windowWidth="24870" windowHeight="20460" xr2:uid="{FB22F9A6-9212-4FA4-9C6C-9674B77F5971}"/>
   </bookViews>
   <sheets>
     <sheet name="initial_26_Summer" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">initial_26_Summer!$A$1:$F$163</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -55,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="187">
   <si>
     <t>Ranking</t>
   </si>
@@ -435,9 +438,6 @@
     <t>Seal Team Sticks</t>
   </si>
   <si>
-    <t>The Seals</t>
-  </si>
-  <si>
     <t>Seattle Seals</t>
   </si>
   <si>
@@ -544,6 +544,81 @@
   </si>
   <si>
     <t>Redrum</t>
+  </si>
+  <si>
+    <t>Mustangs</t>
+  </si>
+  <si>
+    <t>Banana Blades</t>
+  </si>
+  <si>
+    <t>Thursday Cryptids</t>
+  </si>
+  <si>
+    <t>Division 10B Purple</t>
+  </si>
+  <si>
+    <t>Division 10B Red</t>
+  </si>
+  <si>
+    <t>Puckleberries</t>
+  </si>
+  <si>
+    <t>Pull Tab Bandits</t>
+  </si>
+  <si>
+    <t>Bombers</t>
+  </si>
+  <si>
+    <t>Puget Sound Pigeons</t>
+  </si>
+  <si>
+    <t>Breakers</t>
+  </si>
+  <si>
+    <t>Rainiers</t>
+  </si>
+  <si>
+    <t>Scrooge McPuck</t>
+  </si>
+  <si>
+    <t>Cascadians HC</t>
+  </si>
+  <si>
+    <t>Mad Dawgs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flying Monkeys </t>
+  </si>
+  <si>
+    <t>Seals</t>
+  </si>
+  <si>
+    <t>Dumb Pucks</t>
+  </si>
+  <si>
+    <t>Trash Pandas</t>
+  </si>
+  <si>
+    <t>Cherry Pickers</t>
+  </si>
+  <si>
+    <t>Lumberjacks</t>
+  </si>
+  <si>
+    <t>Bullets</t>
+  </si>
+  <si>
+    <t>Fossils</t>
+  </si>
+  <si>
+    <t>Bandits</t>
+  </si>
+  <si>
+    <t>Mighty Boosh</t>
+  </si>
+  <si>
+    <t>Orcas</t>
   </si>
 </sst>
 </file>
@@ -686,7 +761,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -866,6 +941,30 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1027,11 +1126,28 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1407,12 +1523,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D935EE6-5B9C-4F74-9C70-F47CE547CAED}">
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="10" max="10" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1431,32 +1552,32 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>54</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3022</v>
+        <v>4566</v>
       </c>
       <c r="E2">
         <f>ROUND(D2+$K$2*(_xlfn.XLOOKUP(C2,H:H,I:I)-D2),0)</f>
-        <v>2998</v>
+        <v>4481</v>
       </c>
       <c r="F2">
         <f>E2-D2</f>
-        <v>-24</v>
-      </c>
-      <c r="H2" t="str" cm="1">
-        <f t="array" ref="H2:H24">_xlfn.UNIQUE(C2:C139)</f>
-        <v>5C</v>
+        <v>-85</v>
+      </c>
+      <c r="H2" cm="1">
+        <f t="array" ref="H2:H24">_xlfn.UNIQUE(C2:C163)</f>
+        <v>1</v>
       </c>
       <c r="I2">
         <f>ROUND(AVERAGEIF(C:C,H2,D:D),0)</f>
-        <v>2948</v>
+        <v>4309</v>
       </c>
       <c r="K2">
         <v>0.33</v>
@@ -1464,1285 +1585,1258 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>4566</v>
+        <v>4134</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E66" si="0">ROUND(D3+$K$2*(_xlfn.XLOOKUP(C3,H:H,I:I)-D3),0)</f>
-        <v>4495</v>
+        <f>ROUND(D3+$K$2*(_xlfn.XLOOKUP(C3,H:H,I:I)-D3),0)</f>
+        <v>4192</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F7" si="1">E3-D3</f>
-        <v>-71</v>
+        <f>E3-D3</f>
+        <v>58</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I24" si="2">ROUND(AVERAGEIF(C:C,H3,D:D),0)</f>
-        <v>4351</v>
+        <f>ROUND(AVERAGEIF(C:C,H3,D:D),0)</f>
+        <v>4129</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>53</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3033</v>
+        <v>4359</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>3036</v>
+        <f>ROUND(D4+$K$2*(_xlfn.XLOOKUP(C4,H:H,I:I)-D4),0)</f>
+        <v>4343</v>
       </c>
       <c r="F4">
-        <f t="shared" si="1"/>
-        <v>3</v>
+        <f>E4-D4</f>
+        <v>-16</v>
       </c>
       <c r="H4" t="str">
-        <v>5A</v>
+        <v>10A</v>
       </c>
       <c r="I4">
-        <f t="shared" si="2"/>
-        <v>3041</v>
+        <f>ROUND(AVERAGEIF(C:C,H4,D:D),0)</f>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>137</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>719</v>
+        <v>4624</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>818</v>
+        <f>ROUND(D5+$K$2*(_xlfn.XLOOKUP(C5,H:H,I:I)-D5),0)</f>
+        <v>4520</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
-        <v>99</v>
+        <f>E5-D5</f>
+        <v>-104</v>
       </c>
       <c r="H5" t="str">
-        <v>10A</v>
+        <v>10B</v>
       </c>
       <c r="I5">
-        <f t="shared" si="2"/>
-        <v>1018</v>
+        <f>ROUND(AVERAGEIF(C:C,H5,D:D),0)</f>
+        <v>990</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>4063</v>
+      </c>
+      <c r="E6">
+        <f>ROUND(D6+$K$2*(_xlfn.XLOOKUP(C6,H:H,I:I)-D6),0)</f>
+        <v>4144</v>
+      </c>
+      <c r="F6">
+        <f>E6-D6</f>
         <v>81</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6">
-        <v>2471</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>2471</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="H6" t="str">
-        <v>6C</v>
+        <v>3A</v>
       </c>
       <c r="I6">
-        <f t="shared" si="2"/>
-        <v>2471</v>
+        <f>ROUND(AVERAGEIF(C:C,H6,D:D),0)</f>
+        <v>3924</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>130</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1048</v>
+        <v>4350</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>1038</v>
+        <f>ROUND(D7+$K$2*(_xlfn.XLOOKUP(C7,H:H,I:I)-D7),0)</f>
+        <v>4336</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
-        <v>-10</v>
+        <f>E7-D7</f>
+        <v>-14</v>
       </c>
       <c r="H7" t="str">
-        <v>7A</v>
+        <v>3B</v>
       </c>
       <c r="I7">
-        <f t="shared" si="2"/>
-        <v>2003</v>
+        <f>ROUND(AVERAGEIF(C:C,H7,D:D),0)</f>
+        <v>3684</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>92</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>2131</v>
+        <v>4070</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>2089</v>
+        <f>ROUND(D8+$K$2*(_xlfn.XLOOKUP(C8,H:H,I:I)-D8),0)</f>
+        <v>4149</v>
       </c>
       <c r="F8">
         <f>E8-D8</f>
-        <v>-42</v>
+        <v>79</v>
       </c>
       <c r="H8" t="str">
-        <v>5D</v>
+        <v>4A</v>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
-        <v>2724</v>
+        <f>ROUND(AVERAGEIF(C:C,H8,D:D),0)</f>
+        <v>3465</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>62</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>2788</v>
+        <v>4188</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>2767</v>
+        <f>ROUND(D9+$K$2*(_xlfn.XLOOKUP(C9,H:H,I:I)-D9),0)</f>
+        <v>4169</v>
       </c>
       <c r="F9">
-        <f t="shared" ref="F9:F15" si="3">E9-D9</f>
-        <v>-21</v>
+        <f>E9-D9</f>
+        <v>-19</v>
       </c>
       <c r="H9" t="str">
-        <v>9A</v>
+        <v>4B</v>
       </c>
       <c r="I9">
-        <f t="shared" si="2"/>
-        <v>1509</v>
+        <f>ROUND(AVERAGEIF(C:C,H9,D:D),0)</f>
+        <v>3324</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>112</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1642</v>
+        <v>3972</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>1598</v>
+        <f>ROUND(D10+$K$2*(_xlfn.XLOOKUP(C10,H:H,I:I)-D10),0)</f>
+        <v>4024</v>
       </c>
       <c r="F10">
-        <f t="shared" si="3"/>
-        <v>-44</v>
+        <f>E10-D10</f>
+        <v>52</v>
       </c>
       <c r="H10" t="str">
-        <v>8A</v>
+        <v>4C</v>
       </c>
       <c r="I10">
-        <f t="shared" si="2"/>
-        <v>1686</v>
+        <f>ROUND(AVERAGEIF(C:C,H10,D:D),0)</f>
+        <v>3290</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>110</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>1747</v>
+        <v>4160</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>1727</v>
+        <f>ROUND(D11+$K$2*(_xlfn.XLOOKUP(C11,H:H,I:I)-D11),0)</f>
+        <v>4150</v>
       </c>
       <c r="F11">
-        <f t="shared" si="3"/>
-        <v>-20</v>
+        <f>E11-D11</f>
+        <v>-10</v>
       </c>
       <c r="H11" t="str">
-        <v>7B</v>
+        <v>5A</v>
       </c>
       <c r="I11">
-        <f t="shared" si="2"/>
-        <v>1896</v>
+        <f>ROUND(AVERAGEIF(C:C,H11,D:D),0)</f>
+        <v>3052</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>2510</v>
+        <v>4522</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
-        <v>2497</v>
+        <f>ROUND(D12+$K$2*(_xlfn.XLOOKUP(C12,H:H,I:I)-D12),0)</f>
+        <v>4392</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
-        <v>-13</v>
+        <f>E12-D12</f>
+        <v>-130</v>
       </c>
       <c r="H12" t="str">
-        <v>3A</v>
+        <v>5B</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
-        <v>3936</v>
+        <f>ROUND(AVERAGEIF(C:C,H12,D:D),0)</f>
+        <v>2901</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>98</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>1940</v>
+        <v>3913</v>
       </c>
       <c r="E13">
-        <f t="shared" si="0"/>
-        <v>1925</v>
+        <f>ROUND(D13+$K$2*(_xlfn.XLOOKUP(C13,H:H,I:I)-D13),0)</f>
+        <v>3984</v>
       </c>
       <c r="F13">
-        <f t="shared" si="3"/>
-        <v>-15</v>
+        <f>E13-D13</f>
+        <v>71</v>
       </c>
       <c r="H13" t="str">
-        <v>6A</v>
+        <v>5C</v>
       </c>
       <c r="I13">
-        <f t="shared" si="2"/>
-        <v>2612</v>
+        <f>ROUND(AVERAGEIF(C:C,H13,D:D),0)</f>
+        <v>2925</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>3971</v>
+        <v>3963</v>
       </c>
       <c r="E14">
-        <f t="shared" si="0"/>
-        <v>3959</v>
+        <f>ROUND(D14+$K$2*(_xlfn.XLOOKUP(C14,H:H,I:I)-D14),0)</f>
+        <v>4018</v>
       </c>
       <c r="F14">
-        <f t="shared" si="3"/>
-        <v>-12</v>
+        <f>E14-D14</f>
+        <v>55</v>
       </c>
       <c r="H14" t="str">
-        <v>4A</v>
+        <v>5D</v>
       </c>
       <c r="I14">
-        <f t="shared" si="2"/>
-        <v>3457</v>
+        <f>ROUND(AVERAGEIF(C:C,H14,D:D),0)</f>
+        <v>2772</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>59</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>2888</v>
+        <v>4291</v>
       </c>
       <c r="E15">
-        <f t="shared" si="0"/>
-        <v>2797</v>
+        <f>ROUND(D15+$K$2*(_xlfn.XLOOKUP(C15,H:H,I:I)-D15),0)</f>
+        <v>4238</v>
       </c>
       <c r="F15">
-        <f t="shared" si="3"/>
-        <v>-91</v>
-      </c>
-      <c r="H15">
-        <v>2</v>
+        <f>E15-D15</f>
+        <v>-53</v>
+      </c>
+      <c r="H15" t="str">
+        <v>6A</v>
       </c>
       <c r="I15">
-        <f t="shared" si="2"/>
-        <v>4129</v>
+        <f>ROUND(AVERAGEIF(C:C,H15,D:D),0)</f>
+        <v>2593</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>3170</v>
+        <v>4023</v>
       </c>
       <c r="E16">
-        <f t="shared" si="0"/>
-        <v>3127</v>
+        <f>ROUND(D16+$K$2*(_xlfn.XLOOKUP(C16,H:H,I:I)-D16),0)</f>
+        <v>4058</v>
       </c>
       <c r="F16">
-        <f t="shared" ref="F16" si="4">E16-D16</f>
-        <v>-43</v>
+        <f>E16-D16</f>
+        <v>35</v>
       </c>
       <c r="H16" t="str">
-        <v>3B</v>
+        <v>6B</v>
       </c>
       <c r="I16">
-        <f t="shared" si="2"/>
-        <v>3621</v>
+        <f>ROUND(AVERAGEIF(C:C,H16,D:D),0)</f>
+        <v>2524</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17">
-        <v>3624</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>3569</v>
+        <v>137</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3">
+        <v>719</v>
+      </c>
+      <c r="E17" s="3">
+        <f>ROUND(D17+$K$2*(_xlfn.XLOOKUP(C17,H:H,I:I)-D17),0)</f>
+        <v>763</v>
       </c>
       <c r="F17">
-        <f t="shared" ref="F17:F19" si="5">E17-D17</f>
-        <v>-55</v>
+        <f>E17-D17</f>
+        <v>44</v>
       </c>
       <c r="H17" t="str">
+        <v>6C</v>
+      </c>
+      <c r="I17">
+        <f>ROUND(AVERAGEIF(C:C,H17,D:D),0)</f>
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>699</v>
+      </c>
+      <c r="E18">
+        <f>ROUND(D18+$K$2*(_xlfn.XLOOKUP(C18,H:H,I:I)-D18),0)</f>
+        <v>750</v>
+      </c>
+      <c r="F18">
+        <f>E18-D18</f>
+        <v>51</v>
+      </c>
+      <c r="H18" t="str">
         <v>6D</v>
       </c>
-      <c r="I17">
-        <f t="shared" si="2"/>
-        <v>2294</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>4188</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>4169</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="5"/>
-        <v>-19</v>
-      </c>
-      <c r="H18" t="str">
-        <v>4C</v>
-      </c>
       <c r="I18">
-        <f t="shared" si="2"/>
-        <v>3261</v>
+        <f>ROUND(AVERAGEIF(C:C,H18,D:D),0)</f>
+        <v>2426</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>29</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
+        <v>130</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D19">
-        <v>3450</v>
+        <v>1048</v>
       </c>
       <c r="E19">
-        <f t="shared" si="0"/>
-        <v>3506</v>
+        <f>ROUND(D19+$K$2*(_xlfn.XLOOKUP(C19,H:H,I:I)-D19),0)</f>
+        <v>984</v>
       </c>
       <c r="F19">
-        <f t="shared" si="5"/>
-        <v>56</v>
+        <f>E19-D19</f>
+        <v>-64</v>
       </c>
       <c r="H19" t="str">
-        <v>4B</v>
+        <v>7A</v>
       </c>
       <c r="I19">
-        <f t="shared" si="2"/>
-        <v>3324</v>
+        <f>ROUND(AVERAGEIF(C:C,H19,D:D),0)</f>
+        <v>2119</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>82</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20">
-        <v>2403</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>2367</v>
+        <v>135</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3">
+        <v>945</v>
+      </c>
+      <c r="E20" s="3">
+        <f>ROUND(D20+$K$2*(_xlfn.XLOOKUP(C20,H:H,I:I)-D20),0)</f>
+        <v>915</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20" si="6">E20-D20</f>
-        <v>-36</v>
+        <f>E20-D20</f>
+        <v>-30</v>
       </c>
       <c r="H20" t="str">
-        <v>10B</v>
+        <v>7B</v>
       </c>
       <c r="I20">
-        <f t="shared" si="2"/>
-        <v>990</v>
+        <f>ROUND(AVERAGEIF(C:C,H20,D:D),0)</f>
+        <v>1896</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
+        <v>131</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="D21">
-        <v>3377</v>
+        <v>993</v>
       </c>
       <c r="E21">
-        <f t="shared" si="0"/>
-        <v>3458</v>
+        <f>ROUND(D21+$K$2*(_xlfn.XLOOKUP(C21,H:H,I:I)-D21),0)</f>
+        <v>992</v>
       </c>
       <c r="F21">
-        <f t="shared" ref="F21:F25" si="7">E21-D21</f>
-        <v>81</v>
+        <f>E21-D21</f>
+        <v>-1</v>
       </c>
       <c r="H21" t="str">
-        <v>6B</v>
+        <v>8A</v>
       </c>
       <c r="I21">
-        <f t="shared" si="2"/>
-        <v>2549</v>
+        <f>ROUND(AVERAGEIF(C:C,H21,D:D),0)</f>
+        <v>1731</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>49</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
+        <v>136</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="D22">
-        <v>3084</v>
+        <v>864</v>
       </c>
       <c r="E22">
-        <f t="shared" si="0"/>
-        <v>3070</v>
+        <f>ROUND(D22+$K$2*(_xlfn.XLOOKUP(C22,H:H,I:I)-D22),0)</f>
+        <v>906</v>
       </c>
       <c r="F22">
-        <f t="shared" si="7"/>
-        <v>-14</v>
+        <f>E22-D22</f>
+        <v>42</v>
       </c>
       <c r="H22" t="str">
-        <v>9B</v>
+        <v>8B</v>
       </c>
       <c r="I22">
-        <f t="shared" si="2"/>
-        <v>1144</v>
+        <f>ROUND(AVERAGEIF(C:C,H22,D:D),0)</f>
+        <v>1662</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>38</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
+        <v>132</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="D23">
-        <v>3301</v>
+        <v>990</v>
       </c>
       <c r="E23">
-        <f t="shared" si="0"/>
-        <v>3288</v>
+        <f>ROUND(D23+$K$2*(_xlfn.XLOOKUP(C23,H:H,I:I)-D23),0)</f>
+        <v>990</v>
       </c>
       <c r="F23">
-        <f t="shared" si="7"/>
-        <v>-13</v>
+        <f>E23-D23</f>
+        <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v>8B</v>
+        <v>9A</v>
       </c>
       <c r="I23">
-        <f t="shared" si="2"/>
-        <v>1598</v>
+        <f>ROUND(AVERAGEIF(C:C,H23,D:D),0)</f>
+        <v>1418</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
+        <v>138</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="D24">
-        <v>2683</v>
+        <v>605</v>
       </c>
       <c r="E24">
-        <f t="shared" si="0"/>
-        <v>2660</v>
+        <f>ROUND(D24+$K$2*(_xlfn.XLOOKUP(C24,H:H,I:I)-D24),0)</f>
+        <v>732</v>
       </c>
       <c r="F24">
-        <f t="shared" si="7"/>
-        <v>-23</v>
+        <f>E24-D24</f>
+        <v>127</v>
       </c>
       <c r="H24" t="str">
-        <v>5B</v>
+        <v>9B</v>
       </c>
       <c r="I24">
-        <f t="shared" si="2"/>
-        <v>2901</v>
+        <f>ROUND(AVERAGEIF(C:C,H24,D:D),0)</f>
+        <v>1175</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>135</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
+        <v>126</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>104</v>
       </c>
       <c r="D25">
-        <v>945</v>
+        <v>1234</v>
       </c>
       <c r="E25">
-        <f t="shared" si="0"/>
-        <v>969</v>
+        <f>ROUND(D25+$K$2*(_xlfn.XLOOKUP(C25,H:H,I:I)-D25),0)</f>
+        <v>1153</v>
       </c>
       <c r="F25">
-        <f t="shared" si="7"/>
-        <v>24</v>
+        <f>E25-D25</f>
+        <v>-81</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>44</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
+        <v>124</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="D26">
-        <v>3155</v>
+        <v>1251</v>
       </c>
       <c r="E26">
-        <f t="shared" si="0"/>
-        <v>3117</v>
+        <f>ROUND(D26+$K$2*(_xlfn.XLOOKUP(C26,H:H,I:I)-D26),0)</f>
+        <v>1165</v>
       </c>
       <c r="F26">
-        <f t="shared" ref="F26:F89" si="8">E26-D26</f>
-        <v>-38</v>
+        <f>E26-D26</f>
+        <v>-86</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>10</v>
-      </c>
-      <c r="B27" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27">
-        <v>4120</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="0"/>
-        <v>4059</v>
+      <c r="B27" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="7">
+        <v>990</v>
+      </c>
+      <c r="E27" s="7">
+        <f>ROUND(D27+$K$2*(_xlfn.XLOOKUP(C27,H:H,I:I)-D27),0)</f>
+        <v>990</v>
       </c>
       <c r="F27">
-        <f t="shared" ref="F27:F31" si="9">E27-D27</f>
-        <v>-61</v>
+        <f>E27-D27</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>34</v>
-      </c>
-      <c r="B28" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28">
-        <v>3355</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="0"/>
-        <v>3345</v>
+      <c r="B28" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="7">
+        <v>990</v>
+      </c>
+      <c r="E28" s="7">
+        <f>ROUND(D28+$K$2*(_xlfn.XLOOKUP(C28,H:H,I:I)-D28),0)</f>
+        <v>990</v>
       </c>
       <c r="F28">
-        <f t="shared" si="9"/>
-        <v>-10</v>
+        <f>E28-D28</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>4134</v>
-      </c>
-      <c r="E29">
-        <f t="shared" si="0"/>
-        <v>4206</v>
+      <c r="B29" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="7">
+        <v>990</v>
+      </c>
+      <c r="E29" s="7">
+        <f>ROUND(D29+$K$2*(_xlfn.XLOOKUP(C29,H:H,I:I)-D29),0)</f>
+        <v>990</v>
       </c>
       <c r="F29">
-        <f t="shared" si="9"/>
-        <v>72</v>
+        <f>E29-D29</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30">
-        <v>4359</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="0"/>
-        <v>4356</v>
+        <v>14</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3971</v>
+      </c>
+      <c r="E30" s="3">
+        <f>ROUND(D30+$K$2*(_xlfn.XLOOKUP(C30,H:H,I:I)-D30),0)</f>
+        <v>3955</v>
       </c>
       <c r="F30">
-        <f t="shared" si="9"/>
-        <v>-3</v>
+        <f>E30-D30</f>
+        <v>-16</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127</v>
-      </c>
-      <c r="B31" t="s">
-        <v>51</v>
+        <v>10</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>1211</v>
+        <v>4120</v>
       </c>
       <c r="E31">
-        <f t="shared" si="0"/>
-        <v>1309</v>
+        <f>ROUND(D31+$K$2*(_xlfn.XLOOKUP(C31,H:H,I:I)-D31),0)</f>
+        <v>4055</v>
       </c>
       <c r="F31">
-        <f t="shared" si="9"/>
-        <v>98</v>
+        <f>E31-D31</f>
+        <v>-65</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>3972</v>
+        <v>3722</v>
       </c>
       <c r="E32">
-        <f t="shared" si="0"/>
-        <v>4024</v>
+        <f>ROUND(D32+$K$2*(_xlfn.XLOOKUP(C32,H:H,I:I)-D32),0)</f>
+        <v>3789</v>
       </c>
       <c r="F32">
-        <f t="shared" si="8"/>
-        <v>52</v>
+        <f>E32-D32</f>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>45</v>
-      </c>
-      <c r="B33" t="s">
-        <v>53</v>
+        <v>20</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>3148</v>
+        <v>3761</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
-        <v>3082</v>
+        <f>ROUND(D33+$K$2*(_xlfn.XLOOKUP(C33,H:H,I:I)-D33),0)</f>
+        <v>3815</v>
       </c>
       <c r="F33">
-        <f t="shared" ref="F33:F37" si="10">E33-D33</f>
-        <v>-66</v>
+        <f>E33-D33</f>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>91</v>
-      </c>
-      <c r="B34" t="s">
-        <v>54</v>
+        <v>11</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D34">
-        <v>2193</v>
+        <v>4116</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
-        <v>2130</v>
+        <f>ROUND(D34+$K$2*(_xlfn.XLOOKUP(C34,H:H,I:I)-D34),0)</f>
+        <v>4053</v>
       </c>
       <c r="F34">
-        <f t="shared" si="10"/>
+        <f>E34-D34</f>
         <v>-63</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>55</v>
+        <v>17</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D35">
-        <v>2523</v>
+        <v>3925</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
-        <v>2589</v>
+        <f>ROUND(D35+$K$2*(_xlfn.XLOOKUP(C35,H:H,I:I)-D35),0)</f>
+        <v>3925</v>
       </c>
       <c r="F35">
-        <f t="shared" si="10"/>
-        <v>66</v>
+        <f>E35-D35</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>131</v>
-      </c>
-      <c r="B36" t="s">
-        <v>161</v>
+      <c r="B36" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="D36">
-        <v>993</v>
+        <v>4046</v>
       </c>
       <c r="E36">
-        <f t="shared" si="0"/>
-        <v>992</v>
+        <f>ROUND(D36+$K$2*(_xlfn.XLOOKUP(C36,H:H,I:I)-D36),0)</f>
+        <v>4006</v>
       </c>
       <c r="F36">
-        <f t="shared" si="10"/>
-        <v>-1</v>
+        <f>E36-D36</f>
+        <v>-40</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>113</v>
-      </c>
-      <c r="B37" t="s">
-        <v>56</v>
+      <c r="B37" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D37">
-        <v>1607</v>
+        <v>3733</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
-        <v>1633</v>
+        <f>ROUND(D37+$K$2*(_xlfn.XLOOKUP(C37,H:H,I:I)-D37),0)</f>
+        <v>3796</v>
       </c>
       <c r="F37">
-        <f t="shared" si="10"/>
-        <v>26</v>
+        <f>E37-D37</f>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>57</v>
+        <v>29</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D38">
-        <v>3725</v>
+        <v>3450</v>
       </c>
       <c r="E38">
-        <f t="shared" si="0"/>
-        <v>3691</v>
+        <f>ROUND(D38+$K$2*(_xlfn.XLOOKUP(C38,H:H,I:I)-D38),0)</f>
+        <v>3527</v>
       </c>
       <c r="F38">
-        <f t="shared" si="8"/>
-        <v>-34</v>
+        <f>E38-D38</f>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>43</v>
-      </c>
-      <c r="B39" t="s">
-        <v>58</v>
+        <v>21</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D39">
-        <v>3160</v>
+        <v>3725</v>
       </c>
       <c r="E39">
-        <f t="shared" si="0"/>
-        <v>3193</v>
+        <f>ROUND(D39+$K$2*(_xlfn.XLOOKUP(C39,H:H,I:I)-D39),0)</f>
+        <v>3711</v>
       </c>
       <c r="F39">
-        <f t="shared" ref="F39:F43" si="11">E39-D39</f>
-        <v>33</v>
+        <f>E39-D39</f>
+        <v>-14</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>84</v>
-      </c>
-      <c r="B40" t="s">
-        <v>59</v>
+        <v>19</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D40">
-        <v>2382</v>
+        <v>3877</v>
       </c>
       <c r="E40">
-        <f t="shared" si="0"/>
-        <v>2437</v>
+        <f>ROUND(D40+$K$2*(_xlfn.XLOOKUP(C40,H:H,I:I)-D40),0)</f>
+        <v>3813</v>
       </c>
       <c r="F40">
-        <f t="shared" si="11"/>
-        <v>55</v>
+        <f>E40-D40</f>
+        <v>-64</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>133</v>
-      </c>
-      <c r="B41" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D41">
-        <v>989</v>
+        <v>3652</v>
       </c>
       <c r="E41">
-        <f t="shared" si="0"/>
-        <v>1040</v>
+        <f>ROUND(D41+$K$2*(_xlfn.XLOOKUP(C41,H:H,I:I)-D41),0)</f>
+        <v>3663</v>
       </c>
       <c r="F41">
-        <f t="shared" si="11"/>
-        <v>51</v>
+        <f>E41-D41</f>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>90</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
+      <c r="B42" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D42">
-        <v>2277</v>
+        <v>3714</v>
       </c>
       <c r="E42">
-        <f t="shared" si="0"/>
-        <v>2367</v>
+        <f>ROUND(D42+$K$2*(_xlfn.XLOOKUP(C42,H:H,I:I)-D42),0)</f>
+        <v>3704</v>
       </c>
       <c r="F42">
-        <f t="shared" si="11"/>
-        <v>90</v>
+        <f>E42-D42</f>
+        <v>-10</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>77</v>
-      </c>
-      <c r="B43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="D43">
-        <v>2535</v>
+        <v>3377</v>
       </c>
       <c r="E43">
-        <f t="shared" si="0"/>
-        <v>2455</v>
+        <f>ROUND(D43+$K$2*(_xlfn.XLOOKUP(C43,H:H,I:I)-D43),0)</f>
+        <v>3406</v>
       </c>
       <c r="F43">
-        <f t="shared" si="11"/>
-        <v>-80</v>
+        <f>E43-D43</f>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>61</v>
-      </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="D44">
-        <v>2809</v>
+        <v>3647</v>
       </c>
       <c r="E44">
-        <f t="shared" si="0"/>
-        <v>2781</v>
+        <f>ROUND(D44+$K$2*(_xlfn.XLOOKUP(C44,H:H,I:I)-D44),0)</f>
+        <v>3587</v>
       </c>
       <c r="F44">
-        <f t="shared" si="8"/>
-        <v>-28</v>
+        <f>E44-D44</f>
+        <v>-60</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>64</v>
-      </c>
-      <c r="B45" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45">
-        <v>2766</v>
-      </c>
-      <c r="E45">
-        <f t="shared" si="0"/>
-        <v>2715</v>
+        <v>25</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="3">
+        <v>3624</v>
+      </c>
+      <c r="E45" s="3">
+        <f>ROUND(D45+$K$2*(_xlfn.XLOOKUP(C45,H:H,I:I)-D45),0)</f>
+        <v>3572</v>
       </c>
       <c r="F45">
-        <f t="shared" ref="F45:F49" si="12">E45-D45</f>
-        <v>-51</v>
+        <f>E45-D45</f>
+        <v>-52</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
-        <v>65</v>
+        <v>36</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D46">
-        <v>3132</v>
+        <v>3343</v>
       </c>
       <c r="E46">
-        <f t="shared" si="0"/>
-        <v>3195</v>
+        <f>ROUND(D46+$K$2*(_xlfn.XLOOKUP(C46,H:H,I:I)-D46),0)</f>
+        <v>3383</v>
       </c>
       <c r="F46">
-        <f t="shared" si="12"/>
-        <v>63</v>
+        <f>E46-D46</f>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>119</v>
-      </c>
-      <c r="B47" t="s">
-        <v>66</v>
+        <v>35</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="D47">
-        <v>1449</v>
+        <v>3346</v>
       </c>
       <c r="E47">
-        <f t="shared" si="0"/>
-        <v>1498</v>
+        <f>ROUND(D47+$K$2*(_xlfn.XLOOKUP(C47,H:H,I:I)-D47),0)</f>
+        <v>3385</v>
       </c>
       <c r="F47">
-        <f t="shared" si="12"/>
-        <v>49</v>
+        <f>E47-D47</f>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
+        <v>26</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B48" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48">
-        <v>1361</v>
-      </c>
-      <c r="E48">
-        <f t="shared" si="0"/>
-        <v>1248</v>
+      <c r="C48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="3">
+        <v>3584</v>
+      </c>
+      <c r="E48" s="3">
+        <f>ROUND(D48+$K$2*(_xlfn.XLOOKUP(C48,H:H,I:I)-D48),0)</f>
+        <v>3545</v>
       </c>
       <c r="F48">
-        <f t="shared" si="12"/>
-        <v>-113</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E48-D48</f>
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>100</v>
-      </c>
-      <c r="B49" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="10">
+        <v>3421</v>
+      </c>
+      <c r="E49" s="10">
+        <f>ROUND(D49+$K$2*(_xlfn.XLOOKUP(C49,H:H,I:I)-D49),0)</f>
+        <v>3436</v>
+      </c>
+      <c r="F49">
+        <f>E49-D49</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>30</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50">
+        <v>3421</v>
+      </c>
+      <c r="E50">
+        <f>ROUND(D50+$K$2*(_xlfn.XLOOKUP(C50,H:H,I:I)-D50),0)</f>
+        <v>3436</v>
+      </c>
+      <c r="F50">
+        <f>E50-D50</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51">
+        <v>3424</v>
+      </c>
+      <c r="E51">
+        <f>ROUND(D51+$K$2*(_xlfn.XLOOKUP(C51,H:H,I:I)-D51),0)</f>
+        <v>3438</v>
+      </c>
+      <c r="F51">
+        <f>E51-D51</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>34</v>
       </c>
-      <c r="D49">
-        <v>1862</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="0"/>
-        <v>1909</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="12"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>80</v>
-      </c>
-      <c r="B50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50">
-        <v>2476</v>
-      </c>
-      <c r="E50">
-        <f t="shared" si="0"/>
-        <v>2521</v>
-      </c>
-      <c r="F50">
-        <f t="shared" si="8"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>51</v>
-      </c>
-      <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D51">
-        <v>3057</v>
-      </c>
-      <c r="E51">
-        <f t="shared" si="0"/>
-        <v>3006</v>
-      </c>
-      <c r="F51">
-        <f t="shared" ref="F51:F55" si="13">E51-D51</f>
-        <v>-51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="B52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52">
+        <v>3355</v>
+      </c>
+      <c r="E52">
+        <f>ROUND(D52+$K$2*(_xlfn.XLOOKUP(C52,H:H,I:I)-D52),0)</f>
+        <v>3345</v>
+      </c>
+      <c r="F52">
+        <f>E52-D52</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>46</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52">
-        <v>2763</v>
-      </c>
-      <c r="E52">
-        <f t="shared" si="0"/>
-        <v>2692</v>
-      </c>
-      <c r="F52">
-        <f t="shared" si="13"/>
-        <v>-71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>107</v>
-      </c>
-      <c r="B53" t="s">
-        <v>73</v>
-      </c>
       <c r="C53" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D53">
-        <v>1778</v>
+        <v>3132</v>
       </c>
       <c r="E53">
-        <f t="shared" si="0"/>
-        <v>1689</v>
+        <f>ROUND(D53+$K$2*(_xlfn.XLOOKUP(C53,H:H,I:I)-D53),0)</f>
+        <v>3195</v>
       </c>
       <c r="F53">
-        <f t="shared" si="13"/>
-        <v>-89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E53-D53</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>37</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -2752,1888 +2846,2401 @@
         <v>3326</v>
       </c>
       <c r="E54">
-        <f t="shared" si="0"/>
+        <f>ROUND(D54+$K$2*(_xlfn.XLOOKUP(C54,H:H,I:I)-D54),0)</f>
         <v>3325</v>
       </c>
       <c r="F54">
-        <f t="shared" si="13"/>
+        <f>E54-D54</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>109</v>
-      </c>
-      <c r="B55" t="s">
-        <v>78</v>
+        <v>27</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D55">
-        <v>1763</v>
+        <v>3548</v>
       </c>
       <c r="E55">
-        <f t="shared" si="0"/>
-        <v>1807</v>
+        <f>ROUND(D55+$K$2*(_xlfn.XLOOKUP(C55,H:H,I:I)-D55),0)</f>
+        <v>3474</v>
       </c>
       <c r="F55">
-        <f t="shared" si="13"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E55-D55</f>
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>106</v>
-      </c>
-      <c r="B56" t="s">
-        <v>75</v>
+        <v>33</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D56">
-        <v>1816</v>
+        <v>3358</v>
       </c>
       <c r="E56">
-        <f t="shared" si="0"/>
-        <v>1878</v>
+        <f>ROUND(D56+$K$2*(_xlfn.XLOOKUP(C56,H:H,I:I)-D56),0)</f>
+        <v>3347</v>
       </c>
       <c r="F56">
-        <f t="shared" si="8"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E56-D56</f>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>27</v>
-      </c>
-      <c r="B57" t="s">
-        <v>76</v>
+        <v>40</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D57">
-        <v>3548</v>
+        <v>3225</v>
       </c>
       <c r="E57">
-        <f t="shared" si="0"/>
-        <v>3474</v>
+        <f>ROUND(D57+$K$2*(_xlfn.XLOOKUP(C57,H:H,I:I)-D57),0)</f>
+        <v>3258</v>
       </c>
       <c r="F57">
-        <f t="shared" ref="F57:F62" si="14">E57-D57</f>
+        <f>E57-D57</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>38</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58">
+        <v>3301</v>
+      </c>
+      <c r="E58">
+        <f>ROUND(D58+$K$2*(_xlfn.XLOOKUP(C58,H:H,I:I)-D58),0)</f>
+        <v>3297</v>
+      </c>
+      <c r="F58">
+        <f>E58-D58</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>43</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D59">
+        <v>3160</v>
+      </c>
+      <c r="E59">
+        <f>ROUND(D59+$K$2*(_xlfn.XLOOKUP(C59,H:H,I:I)-D59),0)</f>
+        <v>3203</v>
+      </c>
+      <c r="F59">
+        <f>E59-D59</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>28</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60">
+        <v>3518</v>
+      </c>
+      <c r="E60">
+        <f>ROUND(D60+$K$2*(_xlfn.XLOOKUP(C60,H:H,I:I)-D60),0)</f>
+        <v>3443</v>
+      </c>
+      <c r="F60">
+        <f>E60-D60</f>
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>41</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61">
+        <v>3173</v>
+      </c>
+      <c r="E61">
+        <f>ROUND(D61+$K$2*(_xlfn.XLOOKUP(C61,H:H,I:I)-D61),0)</f>
+        <v>3212</v>
+      </c>
+      <c r="F61">
+        <f>E61-D61</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>39</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>3298</v>
+      </c>
+      <c r="E62">
+        <f>ROUND(D62+$K$2*(_xlfn.XLOOKUP(C62,H:H,I:I)-D62),0)</f>
+        <v>3295</v>
+      </c>
+      <c r="F62">
+        <f>E62-D62</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>48</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63">
+        <v>3117</v>
+      </c>
+      <c r="E63">
+        <f>ROUND(D63+$K$2*(_xlfn.XLOOKUP(C63,H:H,I:I)-D63),0)</f>
+        <v>3096</v>
+      </c>
+      <c r="F63">
+        <f>E63-D63</f>
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>53</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3">
+        <v>3033</v>
+      </c>
+      <c r="E64" s="3">
+        <f>ROUND(D64+$K$2*(_xlfn.XLOOKUP(C64,H:H,I:I)-D64),0)</f>
+        <v>3039</v>
+      </c>
+      <c r="F64">
+        <f>E64-D64</f>
+        <v>6</v>
+      </c>
+      <c r="G64" t="str">
+        <f>_xlfn.XLOOKUP(B64,J:J,S:S,"Missing")</f>
+        <v>Missing</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>42</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>3170</v>
+      </c>
+      <c r="E65">
+        <f>ROUND(D65+$K$2*(_xlfn.XLOOKUP(C65,H:H,I:I)-D65),0)</f>
+        <v>3131</v>
+      </c>
+      <c r="F65">
+        <f>E65-D65</f>
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>49</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66">
+        <v>3084</v>
+      </c>
+      <c r="E66">
+        <f>ROUND(D66+$K$2*(_xlfn.XLOOKUP(C66,H:H,I:I)-D66),0)</f>
+        <v>3073</v>
+      </c>
+      <c r="F66">
+        <f>E66-D66</f>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>44</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67">
+        <v>3155</v>
+      </c>
+      <c r="E67">
+        <f>ROUND(D67+$K$2*(_xlfn.XLOOKUP(C67,H:H,I:I)-D67),0)</f>
+        <v>3121</v>
+      </c>
+      <c r="F67">
+        <f>E67-D67</f>
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68">
+        <v>2755</v>
+      </c>
+      <c r="E68">
+        <f>ROUND(D68+$K$2*(_xlfn.XLOOKUP(C68,H:H,I:I)-D68),0)</f>
+        <v>2853</v>
+      </c>
+      <c r="F68">
+        <f>E68-D68</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>52</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69">
+        <v>3049</v>
+      </c>
+      <c r="E69">
+        <f>ROUND(D69+$K$2*(_xlfn.XLOOKUP(C69,H:H,I:I)-D69),0)</f>
+        <v>3050</v>
+      </c>
+      <c r="F69">
+        <f>E69-D69</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>51</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70">
+        <v>3057</v>
+      </c>
+      <c r="E70">
+        <f>ROUND(D70+$K$2*(_xlfn.XLOOKUP(C70,H:H,I:I)-D70),0)</f>
+        <v>3006</v>
+      </c>
+      <c r="F70">
+        <f>E70-D70</f>
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>58</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" s="3">
+        <v>2904</v>
+      </c>
+      <c r="E71" s="3">
+        <f>ROUND(D71+$K$2*(_xlfn.XLOOKUP(C71,H:H,I:I)-D71),0)</f>
+        <v>2903</v>
+      </c>
+      <c r="F71">
+        <f>E71-D71</f>
+        <v>-1</v>
+      </c>
+      <c r="G71" t="str">
+        <f>_xlfn.XLOOKUP(B71,J:J,S:S,"Missing")</f>
+        <v>Missing</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>68</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D72">
+        <v>2726</v>
+      </c>
+      <c r="E72">
+        <f>ROUND(D72+$K$2*(_xlfn.XLOOKUP(C72,H:H,I:I)-D72),0)</f>
+        <v>2784</v>
+      </c>
+      <c r="F72">
+        <f>E72-D72</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>63</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73">
+        <v>2784</v>
+      </c>
+      <c r="E73">
+        <f>ROUND(D73+$K$2*(_xlfn.XLOOKUP(C73,H:H,I:I)-D73),0)</f>
+        <v>2823</v>
+      </c>
+      <c r="F73">
+        <f>E73-D73</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>50</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74">
+        <v>3081</v>
+      </c>
+      <c r="E74">
+        <f>ROUND(D74+$K$2*(_xlfn.XLOOKUP(C74,H:H,I:I)-D74),0)</f>
+        <v>3022</v>
+      </c>
+      <c r="F74">
+        <f>E74-D74</f>
+        <v>-59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>60</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" s="3">
+        <v>2853</v>
+      </c>
+      <c r="E75" s="3">
+        <f>ROUND(D75+$K$2*(_xlfn.XLOOKUP(C75,H:H,I:I)-D75),0)</f>
+        <v>2869</v>
+      </c>
+      <c r="F75">
+        <f>E75-D75</f>
+        <v>16</v>
+      </c>
+      <c r="G75" t="str">
+        <f>_xlfn.XLOOKUP(B75,J:J,S:S,"Missing")</f>
+        <v>Missing</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>54</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76">
+        <v>3022</v>
+      </c>
+      <c r="E76">
+        <f>ROUND(D76+$K$2*(_xlfn.XLOOKUP(C76,H:H,I:I)-D76),0)</f>
+        <v>2990</v>
+      </c>
+      <c r="F76">
+        <f>E76-D76</f>
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>45</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="3">
+        <v>3148</v>
+      </c>
+      <c r="E77" s="3">
+        <f>ROUND(D77+$K$2*(_xlfn.XLOOKUP(C77,H:H,I:I)-D77),0)</f>
+        <v>3074</v>
+      </c>
+      <c r="F77">
+        <f>E77-D77</f>
         <v>-74</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>95</v>
-      </c>
-      <c r="B58" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58">
-        <v>2052</v>
-      </c>
-      <c r="E58">
-        <f t="shared" si="0"/>
-        <v>2036</v>
-      </c>
-      <c r="F58">
-        <f t="shared" si="14"/>
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>136</v>
-      </c>
-      <c r="B59" t="s">
-        <v>141</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D59">
-        <v>864</v>
-      </c>
-      <c r="E59">
-        <f t="shared" si="0"/>
-        <v>906</v>
-      </c>
-      <c r="F59">
-        <f t="shared" si="14"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>132</v>
-      </c>
-      <c r="B60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D60">
-        <v>990</v>
-      </c>
-      <c r="E60">
-        <f t="shared" si="0"/>
-        <v>990</v>
-      </c>
-      <c r="F60">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>36</v>
-      </c>
-      <c r="B61" t="s">
-        <v>79</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D61">
-        <v>3343</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="0"/>
-        <v>3381</v>
-      </c>
-      <c r="F61">
-        <f t="shared" si="14"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>8</v>
-      </c>
-      <c r="B62" t="s">
-        <v>80</v>
-      </c>
-      <c r="C62" s="1">
-        <v>2</v>
-      </c>
-      <c r="D62">
-        <v>4160</v>
-      </c>
-      <c r="E62">
-        <f t="shared" si="0"/>
-        <v>4150</v>
-      </c>
-      <c r="F62">
-        <f t="shared" si="14"/>
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="G77" t="str">
+        <f>_xlfn.XLOOKUP(B77,J:J,S:S,"Missing")</f>
+        <v>Missing</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>72</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B78" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D63">
+      <c r="D78">
         <v>2615</v>
       </c>
-      <c r="E63">
-        <f t="shared" si="0"/>
-        <v>2725</v>
-      </c>
-      <c r="F63">
-        <f t="shared" ref="F63:F67" si="15">E63-D63</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64">
+      <c r="E78">
+        <f>ROUND(D78+$K$2*(_xlfn.XLOOKUP(C78,H:H,I:I)-D78),0)</f>
+        <v>2717</v>
+      </c>
+      <c r="F78">
+        <f>E78-D78</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>57</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B64" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D64">
-        <v>3358</v>
-      </c>
-      <c r="E64">
-        <f t="shared" si="0"/>
-        <v>3347</v>
-      </c>
-      <c r="F64">
-        <f t="shared" si="15"/>
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>117</v>
-      </c>
-      <c r="B65" t="s">
-        <v>83</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D65">
-        <v>1516</v>
-      </c>
-      <c r="E65">
-        <f t="shared" si="0"/>
-        <v>1514</v>
-      </c>
-      <c r="F65">
-        <f t="shared" si="15"/>
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>1</v>
-      </c>
-      <c r="B66" t="s">
-        <v>84</v>
-      </c>
-      <c r="C66" s="1">
-        <v>1</v>
-      </c>
-      <c r="D66">
-        <v>4624</v>
-      </c>
-      <c r="E66">
-        <f t="shared" si="0"/>
-        <v>4534</v>
-      </c>
-      <c r="F66">
-        <f t="shared" si="15"/>
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>22</v>
-      </c>
-      <c r="B67" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67">
-        <v>3722</v>
-      </c>
-      <c r="E67">
-        <f t="shared" ref="E67:E130" si="16">ROUND(D67+$K$2*(_xlfn.XLOOKUP(C67,H:H,I:I)-D67),0)</f>
-        <v>3793</v>
-      </c>
-      <c r="F67">
-        <f t="shared" si="15"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>83</v>
-      </c>
-      <c r="B68" t="s">
-        <v>86</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68">
-        <v>2397</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="16"/>
-        <v>2505</v>
-      </c>
-      <c r="F68">
-        <f t="shared" si="8"/>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>67</v>
-      </c>
-      <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69">
-        <v>2746</v>
-      </c>
-      <c r="E69">
-        <f t="shared" si="16"/>
-        <v>2681</v>
-      </c>
-      <c r="F69">
-        <f t="shared" si="8"/>
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>48</v>
-      </c>
-      <c r="B70" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D70">
-        <v>3117</v>
-      </c>
-      <c r="E70">
-        <f t="shared" si="16"/>
-        <v>3165</v>
-      </c>
-      <c r="F70">
-        <f t="shared" si="8"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>73</v>
-      </c>
-      <c r="B71" t="s">
-        <v>89</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D71">
-        <v>2591</v>
-      </c>
-      <c r="E71">
-        <f t="shared" si="16"/>
-        <v>2551</v>
-      </c>
-      <c r="F71">
-        <f t="shared" si="8"/>
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>35</v>
-      </c>
-      <c r="B72" t="s">
-        <v>90</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D72">
-        <v>3346</v>
-      </c>
-      <c r="E72">
-        <f t="shared" si="16"/>
-        <v>3383</v>
-      </c>
-      <c r="F72">
-        <f t="shared" si="8"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>102</v>
-      </c>
-      <c r="B73" t="s">
-        <v>91</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73">
-        <v>1849</v>
-      </c>
-      <c r="E73">
-        <f t="shared" si="16"/>
-        <v>1865</v>
-      </c>
-      <c r="F73">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>3</v>
-      </c>
-      <c r="B74" t="s">
-        <v>92</v>
-      </c>
-      <c r="C74" s="1">
-        <v>2</v>
-      </c>
-      <c r="D74">
-        <v>4522</v>
-      </c>
-      <c r="E74">
-        <f t="shared" si="16"/>
-        <v>4392</v>
-      </c>
-      <c r="F74">
-        <f t="shared" si="8"/>
-        <v>-130</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>66</v>
-      </c>
-      <c r="B75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C75" s="1" t="s">
+      <c r="D79">
+        <v>2905</v>
+      </c>
+      <c r="E79">
+        <f>ROUND(D79+$K$2*(_xlfn.XLOOKUP(C79,H:H,I:I)-D79),0)</f>
+        <v>2912</v>
+      </c>
+      <c r="F79">
+        <f>E79-D79</f>
         <v>7</v>
       </c>
-      <c r="D75">
-        <v>2755</v>
-      </c>
-      <c r="E75">
-        <f t="shared" si="16"/>
-        <v>2849</v>
-      </c>
-      <c r="F75">
-        <f t="shared" si="8"/>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>86</v>
-      </c>
-      <c r="B76" t="s">
-        <v>94</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76">
-        <v>2317</v>
-      </c>
-      <c r="E76">
-        <f t="shared" si="16"/>
-        <v>2309</v>
-      </c>
-      <c r="F76">
-        <f t="shared" si="8"/>
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>5</v>
-      </c>
-      <c r="B77" t="s">
-        <v>95</v>
-      </c>
-      <c r="C77" s="1">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>4350</v>
-      </c>
-      <c r="E77">
-        <f t="shared" si="16"/>
-        <v>4350</v>
-      </c>
-      <c r="F77">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>58</v>
-      </c>
-      <c r="B78" t="s">
-        <v>96</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D78">
-        <v>2904</v>
-      </c>
-      <c r="E78">
-        <f t="shared" si="16"/>
-        <v>2903</v>
-      </c>
-      <c r="F78">
-        <f t="shared" si="8"/>
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>114</v>
-      </c>
-      <c r="B79" t="s">
-        <v>98</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D79">
-        <v>1605</v>
-      </c>
-      <c r="E79">
-        <f t="shared" si="16"/>
-        <v>1573</v>
-      </c>
-      <c r="F79">
-        <f t="shared" si="8"/>
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>18</v>
-      </c>
-      <c r="B80" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" s="1">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D80">
-        <v>3913</v>
+        <v>2996</v>
       </c>
       <c r="E80">
-        <f t="shared" si="16"/>
-        <v>3984</v>
+        <f>ROUND(D80+$K$2*(_xlfn.XLOOKUP(C80,H:H,I:I)-D80),0)</f>
+        <v>2973</v>
       </c>
       <c r="F80">
-        <f t="shared" si="8"/>
-        <v>71</v>
+        <f>E80-D80</f>
+        <v>-23</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>57</v>
-      </c>
-      <c r="B81" t="s">
-        <v>100</v>
+        <v>55</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D81">
-        <v>2905</v>
+        <v>3002</v>
       </c>
       <c r="E81">
-        <f t="shared" si="16"/>
-        <v>2919</v>
+        <f>ROUND(D81+$K$2*(_xlfn.XLOOKUP(C81,H:H,I:I)-D81),0)</f>
+        <v>2977</v>
       </c>
       <c r="F81">
-        <f t="shared" si="8"/>
-        <v>14</v>
+        <f>E81-D81</f>
+        <v>-25</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>105</v>
-      </c>
-      <c r="B82" t="s">
-        <v>102</v>
+      <c r="B82" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D82">
-        <v>1826</v>
+        <v>2785</v>
       </c>
       <c r="E82">
-        <f t="shared" si="16"/>
-        <v>1780</v>
+        <f>ROUND(D82+$K$2*(_xlfn.XLOOKUP(C82,H:H,I:I)-D82),0)</f>
+        <v>2831</v>
       </c>
       <c r="F82">
-        <f t="shared" si="8"/>
-        <v>-46</v>
+        <f>E82-D82</f>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>20</v>
-      </c>
-      <c r="B83" t="s">
-        <v>103</v>
+        <v>62</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D83">
-        <v>3761</v>
+        <v>2788</v>
       </c>
       <c r="E83">
-        <f t="shared" si="16"/>
-        <v>3819</v>
+        <f>ROUND(D83+$K$2*(_xlfn.XLOOKUP(C83,H:H,I:I)-D83),0)</f>
+        <v>2783</v>
       </c>
       <c r="F83">
-        <f t="shared" si="8"/>
-        <v>58</v>
+        <f>E83-D83</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>125</v>
-      </c>
-      <c r="B84" t="s">
-        <v>105</v>
+        <v>78</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D84">
-        <v>1240</v>
+        <v>2523</v>
       </c>
       <c r="E84">
-        <f t="shared" si="16"/>
-        <v>1208</v>
+        <f>ROUND(D84+$K$2*(_xlfn.XLOOKUP(C84,H:H,I:I)-D84),0)</f>
+        <v>2605</v>
       </c>
       <c r="F84">
-        <f t="shared" si="8"/>
-        <v>-32</v>
+        <f>E84-D84</f>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>120</v>
-      </c>
-      <c r="B85" t="s">
-        <v>106</v>
+        <v>61</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="D85">
-        <v>1366</v>
+        <v>2809</v>
       </c>
       <c r="E85">
-        <f t="shared" si="16"/>
-        <v>1443</v>
+        <f>ROUND(D85+$K$2*(_xlfn.XLOOKUP(C85,H:H,I:I)-D85),0)</f>
+        <v>2797</v>
       </c>
       <c r="F85">
-        <f t="shared" si="8"/>
-        <v>77</v>
+        <f>E85-D85</f>
+        <v>-12</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>69</v>
-      </c>
-      <c r="B86" t="s">
-        <v>107</v>
+        <v>83</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D86">
-        <v>2701</v>
+        <v>2397</v>
       </c>
       <c r="E86">
-        <f t="shared" si="16"/>
-        <v>2709</v>
+        <f>ROUND(D86+$K$2*(_xlfn.XLOOKUP(C86,H:H,I:I)-D86),0)</f>
+        <v>2521</v>
       </c>
       <c r="F86">
-        <f t="shared" si="8"/>
-        <v>8</v>
+        <f>E86-D86</f>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>101</v>
-      </c>
-      <c r="B87" t="s">
-        <v>101</v>
+        <v>69</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="D87">
-        <v>1850</v>
+        <v>2701</v>
       </c>
       <c r="E87">
-        <f t="shared" si="16"/>
-        <v>1767</v>
+        <f>ROUND(D87+$K$2*(_xlfn.XLOOKUP(C87,H:H,I:I)-D87),0)</f>
+        <v>2724</v>
       </c>
       <c r="F87">
-        <f t="shared" si="8"/>
-        <v>-83</v>
+        <f>E87-D87</f>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>97</v>
-      </c>
-      <c r="B88" t="s">
-        <v>108</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D88">
-        <v>1966</v>
-      </c>
-      <c r="E88">
-        <f t="shared" si="16"/>
-        <v>1978</v>
+        <v>47</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="10">
+        <v>3125</v>
+      </c>
+      <c r="E88" s="10">
+        <f>ROUND(D88+$K$2*(_xlfn.XLOOKUP(C88,H:H,I:I)-D88),0)</f>
+        <v>3009</v>
       </c>
       <c r="F88">
-        <f t="shared" si="8"/>
-        <v>12</v>
+        <f>E88-D88</f>
+        <v>-116</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>87</v>
-      </c>
-      <c r="B89" t="s">
-        <v>109</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>40</v>
+        <v>59</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="D89">
-        <v>2304</v>
+        <v>2888</v>
       </c>
       <c r="E89">
-        <f t="shared" si="16"/>
-        <v>2359</v>
+        <f>ROUND(D89+$K$2*(_xlfn.XLOOKUP(C89,H:H,I:I)-D89),0)</f>
+        <v>2850</v>
       </c>
       <c r="F89">
-        <f t="shared" si="8"/>
-        <v>55</v>
+        <f>E89-D89</f>
+        <v>-38</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>76</v>
-      </c>
-      <c r="B90" t="s">
-        <v>110</v>
+      <c r="B90" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D90">
-        <v>2544</v>
+        <v>2942</v>
       </c>
       <c r="E90">
-        <f t="shared" si="16"/>
-        <v>2546</v>
+        <f>ROUND(D90+$K$2*(_xlfn.XLOOKUP(C90,H:H,I:I)-D90),0)</f>
+        <v>2886</v>
       </c>
       <c r="F90">
-        <f t="shared" ref="F90:F139" si="17">E90-D90</f>
-        <v>2</v>
+        <f>E90-D90</f>
+        <v>-56</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>122</v>
-      </c>
-      <c r="B91" t="s">
-        <v>111</v>
+        <v>70</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D91">
-        <v>1348</v>
+        <v>2683</v>
       </c>
       <c r="E91">
-        <f t="shared" si="16"/>
-        <v>1281</v>
+        <f>ROUND(D91+$K$2*(_xlfn.XLOOKUP(C91,H:H,I:I)-D91),0)</f>
+        <v>2653</v>
       </c>
       <c r="F91">
-        <f t="shared" si="17"/>
-        <v>-67</v>
+        <f>E91-D91</f>
+        <v>-30</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>85</v>
-      </c>
-      <c r="B92" t="s">
-        <v>112</v>
+        <v>64</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D92">
-        <v>2344</v>
+        <v>2766</v>
       </c>
       <c r="E92">
-        <f t="shared" si="16"/>
-        <v>2328</v>
+        <f>ROUND(D92+$K$2*(_xlfn.XLOOKUP(C92,H:H,I:I)-D92),0)</f>
+        <v>2709</v>
       </c>
       <c r="F92">
-        <f t="shared" si="17"/>
-        <v>-16</v>
+        <f>E92-D92</f>
+        <v>-57</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>68</v>
-      </c>
-      <c r="B93" t="s">
-        <v>113</v>
+        <v>80</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="D93">
-        <v>2726</v>
+        <v>2476</v>
       </c>
       <c r="E93">
-        <f t="shared" si="16"/>
-        <v>2784</v>
+        <f>ROUND(D93+$K$2*(_xlfn.XLOOKUP(C93,H:H,I:I)-D93),0)</f>
+        <v>2515</v>
       </c>
       <c r="F93">
-        <f t="shared" si="17"/>
-        <v>58</v>
+        <f>E93-D93</f>
+        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>16</v>
-      </c>
-      <c r="B94" t="s">
-        <v>114</v>
-      </c>
-      <c r="C94" s="1">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="D94">
-        <v>3963</v>
+        <v>2572</v>
       </c>
       <c r="E94">
-        <f t="shared" si="16"/>
-        <v>4018</v>
+        <f>ROUND(D94+$K$2*(_xlfn.XLOOKUP(C94,H:H,I:I)-D94),0)</f>
+        <v>2579</v>
       </c>
       <c r="F94">
-        <f t="shared" si="17"/>
-        <v>55</v>
+        <f>E94-D94</f>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>129</v>
-      </c>
-      <c r="B95" t="s">
-        <v>115</v>
+        <v>88</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D95">
-        <v>1095</v>
+        <v>2284</v>
       </c>
       <c r="E95">
-        <f t="shared" si="16"/>
-        <v>1111</v>
+        <f>ROUND(D95+$K$2*(_xlfn.XLOOKUP(C95,H:H,I:I)-D95),0)</f>
+        <v>2386</v>
       </c>
       <c r="F95">
-        <f t="shared" si="17"/>
-        <v>16</v>
+        <f>E95-D95</f>
+        <v>102</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>138</v>
-      </c>
-      <c r="B96" t="s">
-        <v>162</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D96">
-        <v>605</v>
-      </c>
-      <c r="E96">
-        <f t="shared" si="16"/>
-        <v>732</v>
+      <c r="B96" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" s="10">
+        <v>2625</v>
+      </c>
+      <c r="E96" s="10">
+        <f>ROUND(D96+$K$2*(_xlfn.XLOOKUP(C96,H:H,I:I)-D96),0)</f>
+        <v>2614</v>
       </c>
       <c r="F96">
-        <f t="shared" si="17"/>
-        <v>127</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>63</v>
-      </c>
-      <c r="B97" t="s">
-        <v>116</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D97">
-        <v>2784</v>
-      </c>
-      <c r="E97">
-        <f t="shared" si="16"/>
-        <v>2823</v>
+        <f>E96-D96</f>
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B97" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" s="10">
+        <v>2696</v>
+      </c>
+      <c r="E97" s="10">
+        <f>ROUND(D97+$K$2*(_xlfn.XLOOKUP(C97,H:H,I:I)-D97),0)</f>
+        <v>2662</v>
       </c>
       <c r="F97">
-        <f t="shared" si="17"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>11</v>
-      </c>
-      <c r="B98" t="s">
-        <v>117</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D98">
-        <v>4116</v>
-      </c>
-      <c r="E98">
-        <f t="shared" si="16"/>
-        <v>4057</v>
+        <f>E97-D97</f>
+        <v>-34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B98" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" s="10">
+        <v>2640</v>
+      </c>
+      <c r="E98" s="10">
+        <f>ROUND(D98+$K$2*(_xlfn.XLOOKUP(C98,H:H,I:I)-D98),0)</f>
+        <v>2624</v>
       </c>
       <c r="F98">
-        <f t="shared" si="17"/>
-        <v>-59</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E98-D98</f>
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>126</v>
-      </c>
-      <c r="B99" t="s">
-        <v>160</v>
+        <v>84</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D99">
-        <v>1234</v>
+        <v>2382</v>
       </c>
       <c r="E99">
-        <f t="shared" si="16"/>
-        <v>1153</v>
+        <f>ROUND(D99+$K$2*(_xlfn.XLOOKUP(C99,H:H,I:I)-D99),0)</f>
+        <v>2429</v>
       </c>
       <c r="F99">
-        <f t="shared" si="17"/>
-        <v>-81</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E99-D99</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>118</v>
+        <v>90</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D100">
-        <v>1870</v>
+        <v>2277</v>
       </c>
       <c r="E100">
-        <f t="shared" si="16"/>
-        <v>1879</v>
+        <f>ROUND(D100+$K$2*(_xlfn.XLOOKUP(C100,H:H,I:I)-D100),0)</f>
+        <v>2359</v>
       </c>
       <c r="F100">
-        <f t="shared" si="17"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E100-D100</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>24</v>
-      </c>
-      <c r="B101" t="s">
-        <v>119</v>
+        <v>65</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D101">
-        <v>3647</v>
+        <v>2763</v>
       </c>
       <c r="E101">
-        <f t="shared" si="16"/>
-        <v>3638</v>
+        <f>ROUND(D101+$K$2*(_xlfn.XLOOKUP(C101,H:H,I:I)-D101),0)</f>
+        <v>2684</v>
       </c>
       <c r="F101">
-        <f t="shared" si="17"/>
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E101-D101</f>
+        <v>-79</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>19</v>
-      </c>
-      <c r="B102" t="s">
-        <v>120</v>
+        <v>67</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D102">
-        <v>3877</v>
+        <v>2746</v>
       </c>
       <c r="E102">
-        <f t="shared" si="16"/>
-        <v>3793</v>
+        <f>ROUND(D102+$K$2*(_xlfn.XLOOKUP(C102,H:H,I:I)-D102),0)</f>
+        <v>2673</v>
       </c>
       <c r="F102">
-        <f t="shared" si="17"/>
-        <v>-84</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <f>E102-D102</f>
+        <v>-73</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
+        <v>76</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103">
+        <v>2544</v>
+      </c>
+      <c r="E103">
+        <f>ROUND(D103+$K$2*(_xlfn.XLOOKUP(C103,H:H,I:I)-D103),0)</f>
+        <v>2537</v>
+      </c>
+      <c r="F103">
+        <f>E103-D103</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>74</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" s="3">
+        <v>2583</v>
+      </c>
+      <c r="E104" s="3">
+        <f>ROUND(D104+$K$2*(_xlfn.XLOOKUP(C104,H:H,I:I)-D104),0)</f>
+        <v>2564</v>
+      </c>
+      <c r="F104">
+        <f>E104-D104</f>
+        <v>-19</v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" ref="G104:G111" si="0">_xlfn.XLOOKUP(B104,J:J,S:S,"Missing")</f>
+        <v>Missing</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B105" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" s="10">
+        <v>2643</v>
+      </c>
+      <c r="E105" s="10">
+        <f>ROUND(D105+$K$2*(_xlfn.XLOOKUP(C105,H:H,I:I)-D105),0)</f>
+        <v>2604</v>
+      </c>
+      <c r="F105">
+        <f>E105-D105</f>
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B106" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" s="10">
+        <v>2250</v>
+      </c>
+      <c r="E106" s="10">
+        <f>ROUND(D106+$K$2*(_xlfn.XLOOKUP(C106,H:H,I:I)-D106),0)</f>
+        <v>2340</v>
+      </c>
+      <c r="F106">
+        <f>E106-D106</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>81</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B103" t="s">
-        <v>122</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D103">
-        <v>3225</v>
-      </c>
-      <c r="E103">
-        <f t="shared" si="16"/>
-        <v>3258</v>
-      </c>
-      <c r="F103">
-        <f t="shared" si="17"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>26</v>
-      </c>
-      <c r="B104" t="s">
-        <v>121</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D104">
-        <v>3584</v>
-      </c>
-      <c r="E104">
-        <f t="shared" si="16"/>
-        <v>3542</v>
-      </c>
-      <c r="F104">
-        <f t="shared" si="17"/>
-        <v>-42</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>116</v>
-      </c>
-      <c r="B105" t="s">
-        <v>123</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D105">
-        <v>1548</v>
-      </c>
-      <c r="E105">
-        <f t="shared" si="16"/>
-        <v>1565</v>
-      </c>
-      <c r="F105">
-        <f t="shared" si="17"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>50</v>
-      </c>
-      <c r="B106" t="s">
-        <v>124</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D106">
-        <v>3081</v>
-      </c>
-      <c r="E106">
-        <f t="shared" si="16"/>
-        <v>3022</v>
-      </c>
-      <c r="F106">
-        <f t="shared" si="17"/>
-        <v>-59</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>118</v>
-      </c>
-      <c r="B107" t="s">
-        <v>125</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="D107">
-        <v>1491</v>
+        <v>2471</v>
       </c>
       <c r="E107">
-        <f t="shared" si="16"/>
-        <v>1555</v>
+        <f>ROUND(D107+$K$2*(_xlfn.XLOOKUP(C107,H:H,I:I)-D107),0)</f>
+        <v>2471</v>
       </c>
       <c r="F107">
-        <f t="shared" si="17"/>
+        <f>E107-D107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>79</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D108">
+        <v>2510</v>
+      </c>
+      <c r="E108">
+        <f>ROUND(D108+$K$2*(_xlfn.XLOOKUP(C108,H:H,I:I)-D108),0)</f>
+        <v>2497</v>
+      </c>
+      <c r="F108">
+        <f>E108-D108</f>
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>73</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D109">
+        <v>2591</v>
+      </c>
+      <c r="E109">
+        <f>ROUND(D109+$K$2*(_xlfn.XLOOKUP(C109,H:H,I:I)-D109),0)</f>
+        <v>2551</v>
+      </c>
+      <c r="F109">
+        <f>E109-D109</f>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>87</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D110">
+        <v>2304</v>
+      </c>
+      <c r="E110">
+        <f>ROUND(D110+$K$2*(_xlfn.XLOOKUP(C110,H:H,I:I)-D110),0)</f>
+        <v>2359</v>
+      </c>
+      <c r="F110">
+        <f>E110-D110</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>89</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D111" s="3">
+        <v>2276</v>
+      </c>
+      <c r="E111" s="3">
+        <f>ROUND(D111+$K$2*(_xlfn.XLOOKUP(C111,H:H,I:I)-D111),0)</f>
+        <v>2340</v>
+      </c>
+      <c r="F111">
+        <f>E111-D111</f>
         <v>64</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>103</v>
-      </c>
-      <c r="B108" t="s">
-        <v>128</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D108">
-        <v>1848</v>
-      </c>
-      <c r="E108">
-        <f t="shared" si="16"/>
-        <v>1864</v>
-      </c>
-      <c r="F108">
-        <f t="shared" si="17"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>96</v>
-      </c>
-      <c r="B109" t="s">
-        <v>129</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D109">
-        <v>2047</v>
-      </c>
-      <c r="E109">
-        <f t="shared" si="16"/>
-        <v>2129</v>
-      </c>
-      <c r="F109">
-        <f t="shared" si="17"/>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>94</v>
-      </c>
-      <c r="B110" t="s">
-        <v>127</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D110">
-        <v>2104</v>
-      </c>
-      <c r="E110">
-        <f t="shared" si="16"/>
-        <v>2035</v>
-      </c>
-      <c r="F110">
-        <f t="shared" si="17"/>
-        <v>-69</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>104</v>
-      </c>
-      <c r="B111" t="s">
-        <v>130</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D111">
-        <v>1823</v>
-      </c>
-      <c r="E111">
-        <f t="shared" si="16"/>
-        <v>1749</v>
-      </c>
-      <c r="F111">
-        <f t="shared" si="17"/>
-        <v>-74</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G111" t="str">
+        <f t="shared" si="0"/>
+        <v>Missing</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>12</v>
-      </c>
-      <c r="B112" t="s">
-        <v>131</v>
-      </c>
-      <c r="C112" s="1">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D112">
-        <v>4070</v>
+        <v>2676</v>
       </c>
       <c r="E112">
-        <f t="shared" si="16"/>
-        <v>4163</v>
+        <f>ROUND(D112+$K$2*(_xlfn.XLOOKUP(C112,H:H,I:I)-D112),0)</f>
+        <v>2608</v>
       </c>
       <c r="F112">
-        <f t="shared" si="17"/>
-        <v>93</v>
+        <f>E112-D112</f>
+        <v>-68</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>75</v>
-      </c>
-      <c r="B113" t="s">
-        <v>132</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D113">
-        <v>2572</v>
-      </c>
-      <c r="E113">
-        <f t="shared" si="16"/>
-        <v>2585</v>
+      <c r="B113" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D113" s="7">
+        <v>2471</v>
+      </c>
+      <c r="E113" s="7">
+        <f>ROUND(D113+$K$2*(_xlfn.XLOOKUP(C113,H:H,I:I)-D113),0)</f>
+        <v>2471</v>
       </c>
       <c r="F113">
-        <f t="shared" si="17"/>
-        <v>13</v>
+        <f>E113-D113</f>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>23</v>
-      </c>
-      <c r="B114" t="s">
-        <v>133</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D114">
-        <v>3652</v>
-      </c>
-      <c r="E114">
-        <f t="shared" si="16"/>
-        <v>3642</v>
+      <c r="B114" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D114" s="7">
+        <v>2471</v>
+      </c>
+      <c r="E114" s="7">
+        <f>ROUND(D114+$K$2*(_xlfn.XLOOKUP(C114,H:H,I:I)-D114),0)</f>
+        <v>2471</v>
       </c>
       <c r="F114">
-        <f t="shared" si="17"/>
-        <v>-10</v>
+        <f>E114-D114</f>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>31</v>
-      </c>
-      <c r="B115" t="s">
-        <v>134</v>
+        <v>77</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D115">
-        <v>3421</v>
+        <v>2535</v>
       </c>
       <c r="E115">
-        <f t="shared" si="16"/>
-        <v>3433</v>
+        <f>ROUND(D115+$K$2*(_xlfn.XLOOKUP(C115,H:H,I:I)-D115),0)</f>
+        <v>2499</v>
       </c>
       <c r="F115">
-        <f t="shared" si="17"/>
-        <v>12</v>
+        <f>E115-D115</f>
+        <v>-36</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>28</v>
-      </c>
-      <c r="B116" t="s">
-        <v>135</v>
+        <v>86</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D116">
-        <v>3518</v>
+        <v>2317</v>
       </c>
       <c r="E116">
-        <f t="shared" si="16"/>
-        <v>3433</v>
+        <f>ROUND(D116+$K$2*(_xlfn.XLOOKUP(C116,H:H,I:I)-D116),0)</f>
+        <v>2353</v>
       </c>
       <c r="F116">
-        <f t="shared" si="17"/>
-        <v>-85</v>
+        <f>E116-D116</f>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>60</v>
-      </c>
-      <c r="B117" t="s">
-        <v>136</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D117">
-        <v>2853</v>
+        <v>2403</v>
       </c>
       <c r="E117">
-        <f t="shared" si="16"/>
-        <v>2869</v>
+        <f>ROUND(D117+$K$2*(_xlfn.XLOOKUP(C117,H:H,I:I)-D117),0)</f>
+        <v>2309</v>
       </c>
       <c r="F117">
-        <f t="shared" si="17"/>
-        <v>16</v>
+        <f>E117-D117</f>
+        <v>-94</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>108</v>
-      </c>
-      <c r="B118" t="s">
-        <v>138</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>22</v>
+        <v>85</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D118">
-        <v>1775</v>
+        <v>2344</v>
       </c>
       <c r="E118">
-        <f t="shared" si="16"/>
-        <v>1746</v>
+        <f>ROUND(D118+$K$2*(_xlfn.XLOOKUP(C118,H:H,I:I)-D118),0)</f>
+        <v>2270</v>
       </c>
       <c r="F118">
-        <f t="shared" si="17"/>
-        <v>-29</v>
+        <f>E118-D118</f>
+        <v>-74</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>134</v>
-      </c>
-      <c r="B119" t="s">
-        <v>137</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>16</v>
+        <v>96</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D119">
-        <v>986</v>
+        <v>2047</v>
       </c>
       <c r="E119">
-        <f t="shared" si="16"/>
-        <v>1038</v>
+        <f>ROUND(D119+$K$2*(_xlfn.XLOOKUP(C119,H:H,I:I)-D119),0)</f>
+        <v>2071</v>
       </c>
       <c r="F119">
-        <f t="shared" si="17"/>
-        <v>52</v>
+        <f>E119-D119</f>
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>111</v>
-      </c>
-      <c r="B120" t="s">
-        <v>139</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>22</v>
+        <v>93</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="D120">
-        <v>1667</v>
+        <v>2118</v>
       </c>
       <c r="E120">
-        <f t="shared" si="16"/>
-        <v>1673</v>
+        <f>ROUND(D120+$K$2*(_xlfn.XLOOKUP(C120,H:H,I:I)-D120),0)</f>
+        <v>2118</v>
       </c>
       <c r="F120">
-        <f t="shared" si="17"/>
-        <v>6</v>
+        <f>E120-D120</f>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>88</v>
-      </c>
-      <c r="B121" t="s">
-        <v>143</v>
+        <v>92</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D121">
-        <v>2284</v>
+        <v>2131</v>
       </c>
       <c r="E121">
-        <f t="shared" si="16"/>
-        <v>2392</v>
+        <f>ROUND(D121+$K$2*(_xlfn.XLOOKUP(C121,H:H,I:I)-D121),0)</f>
+        <v>2127</v>
       </c>
       <c r="F121">
-        <f t="shared" si="17"/>
-        <v>108</v>
+        <f>E121-D121</f>
+        <v>-4</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>30</v>
-      </c>
-      <c r="B122" t="s">
-        <v>144</v>
+        <v>91</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D122">
-        <v>3421</v>
+        <v>2193</v>
       </c>
       <c r="E122">
-        <f t="shared" si="16"/>
-        <v>3433</v>
+        <f>ROUND(D122+$K$2*(_xlfn.XLOOKUP(C122,H:H,I:I)-D122),0)</f>
+        <v>2169</v>
       </c>
       <c r="F122">
-        <f t="shared" si="17"/>
-        <v>12</v>
+        <f>E122-D122</f>
+        <v>-24</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>56</v>
-      </c>
-      <c r="B123" t="s">
-        <v>145</v>
+        <v>100</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D123">
-        <v>2996</v>
+        <v>1862</v>
       </c>
       <c r="E123">
-        <f t="shared" si="16"/>
-        <v>2980</v>
+        <f>ROUND(D123+$K$2*(_xlfn.XLOOKUP(C123,H:H,I:I)-D123),0)</f>
+        <v>1947</v>
       </c>
       <c r="F123">
-        <f t="shared" si="17"/>
-        <v>-16</v>
+        <f>E123-D123</f>
+        <v>85</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>124</v>
-      </c>
-      <c r="B124" t="s">
-        <v>142</v>
+        <v>106</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D124">
-        <v>1251</v>
+        <v>1816</v>
       </c>
       <c r="E124">
-        <f t="shared" si="16"/>
-        <v>1165</v>
+        <f>ROUND(D124+$K$2*(_xlfn.XLOOKUP(C124,H:H,I:I)-D124),0)</f>
+        <v>1916</v>
       </c>
       <c r="F124">
-        <f t="shared" si="17"/>
-        <v>-86</v>
+        <f>E124-D124</f>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>6</v>
-      </c>
-      <c r="B125" t="s">
-        <v>146</v>
-      </c>
-      <c r="C125" s="1">
-        <v>2</v>
+        <v>95</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D125">
-        <v>4291</v>
+        <v>2052</v>
       </c>
       <c r="E125">
-        <f t="shared" si="16"/>
-        <v>4238</v>
+        <f>ROUND(D125+$K$2*(_xlfn.XLOOKUP(C125,H:H,I:I)-D125),0)</f>
+        <v>2074</v>
       </c>
       <c r="F125">
-        <f t="shared" si="17"/>
-        <v>-53</v>
+        <f>E125-D125</f>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>17</v>
-      </c>
-      <c r="B126" t="s">
-        <v>147</v>
+        <v>97</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D126">
-        <v>3925</v>
+        <v>1966</v>
       </c>
       <c r="E126">
-        <f t="shared" si="16"/>
-        <v>3929</v>
+        <f>ROUND(D126+$K$2*(_xlfn.XLOOKUP(C126,H:H,I:I)-D126),0)</f>
+        <v>2016</v>
       </c>
       <c r="F126">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f>E126-D126</f>
+        <v>50</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>13</v>
-      </c>
-      <c r="B127" t="s">
-        <v>148</v>
-      </c>
-      <c r="C127" s="1">
-        <v>2</v>
+      <c r="B127" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D127">
-        <v>4023</v>
+        <v>2373</v>
       </c>
       <c r="E127">
-        <f t="shared" si="16"/>
-        <v>4058</v>
+        <f>ROUND(D127+$K$2*(_xlfn.XLOOKUP(C127,H:H,I:I)-D127),0)</f>
+        <v>2289</v>
       </c>
       <c r="F127">
-        <f t="shared" si="17"/>
-        <v>35</v>
+        <f>E127-D127</f>
+        <v>-84</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>47</v>
-      </c>
-      <c r="B128" t="s">
-        <v>126</v>
+        <v>98</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D128">
-        <v>3125</v>
+        <v>1940</v>
       </c>
       <c r="E128">
-        <f t="shared" si="16"/>
-        <v>2993</v>
+        <f>ROUND(D128+$K$2*(_xlfn.XLOOKUP(C128,H:H,I:I)-D128),0)</f>
+        <v>1925</v>
       </c>
       <c r="F128">
-        <f t="shared" si="17"/>
-        <v>-132</v>
+        <f>E128-D128</f>
+        <v>-15</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>115</v>
-      </c>
-      <c r="B129" t="s">
-        <v>149</v>
+        <v>109</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="D129">
-        <v>1552</v>
+        <v>1763</v>
       </c>
       <c r="E129">
-        <f t="shared" si="16"/>
-        <v>1567</v>
+        <f>ROUND(D129+$K$2*(_xlfn.XLOOKUP(C129,H:H,I:I)-D129),0)</f>
+        <v>1807</v>
       </c>
       <c r="F129">
-        <f t="shared" si="17"/>
-        <v>15</v>
+        <f>E129-D129</f>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>41</v>
-      </c>
-      <c r="B130" t="s">
-        <v>150</v>
+        <v>102</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D130">
-        <v>3173</v>
+        <v>1849</v>
       </c>
       <c r="E130">
-        <f t="shared" si="16"/>
-        <v>3202</v>
+        <f>ROUND(D130+$K$2*(_xlfn.XLOOKUP(C130,H:H,I:I)-D130),0)</f>
+        <v>1865</v>
       </c>
       <c r="F130">
-        <f t="shared" si="17"/>
-        <v>29</v>
+        <f>E130-D130</f>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>74</v>
-      </c>
-      <c r="B131" t="s">
-        <v>152</v>
+        <v>99</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D131">
-        <v>2583</v>
+        <v>1870</v>
       </c>
       <c r="E131">
-        <f t="shared" ref="E131:E139" si="18">ROUND(D131+$K$2*(_xlfn.XLOOKUP(C131,H:H,I:I)-D131),0)</f>
-        <v>2572</v>
+        <f>ROUND(D131+$K$2*(_xlfn.XLOOKUP(C131,H:H,I:I)-D131),0)</f>
+        <v>1879</v>
       </c>
       <c r="F131">
-        <f t="shared" si="17"/>
-        <v>-11</v>
+        <f>E131-D131</f>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>89</v>
-      </c>
-      <c r="B132" t="s">
-        <v>151</v>
+        <v>103</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D132">
-        <v>2276</v>
+        <v>1848</v>
       </c>
       <c r="E132">
-        <f t="shared" si="18"/>
-        <v>2340</v>
+        <f>ROUND(D132+$K$2*(_xlfn.XLOOKUP(C132,H:H,I:I)-D132),0)</f>
+        <v>1864</v>
       </c>
       <c r="F132">
-        <f t="shared" si="17"/>
-        <v>64</v>
+        <f>E132-D132</f>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>93</v>
-      </c>
-      <c r="B133" t="s">
-        <v>153</v>
+        <v>94</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D133">
-        <v>2118</v>
+        <v>2104</v>
       </c>
       <c r="E133">
-        <f t="shared" si="18"/>
-        <v>2176</v>
+        <f>ROUND(D133+$K$2*(_xlfn.XLOOKUP(C133,H:H,I:I)-D133),0)</f>
+        <v>2035</v>
       </c>
       <c r="F133">
-        <f t="shared" si="17"/>
-        <v>58</v>
+        <f>E133-D133</f>
+        <v>-69</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>128</v>
-      </c>
-      <c r="B134" t="s">
-        <v>154</v>
+        <v>110</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D134">
-        <v>1207</v>
+        <v>1747</v>
       </c>
       <c r="E134">
-        <f t="shared" si="18"/>
-        <v>1186</v>
+        <f>ROUND(D134+$K$2*(_xlfn.XLOOKUP(C134,H:H,I:I)-D134),0)</f>
+        <v>1742</v>
       </c>
       <c r="F134">
-        <f t="shared" si="17"/>
-        <v>-21</v>
+        <f>E134-D134</f>
+        <v>-5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>52</v>
-      </c>
-      <c r="B135" t="s">
-        <v>155</v>
+        <v>113</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D135">
-        <v>3049</v>
+        <v>1607</v>
       </c>
       <c r="E135">
-        <f t="shared" si="18"/>
-        <v>3046</v>
+        <f>ROUND(D135+$K$2*(_xlfn.XLOOKUP(C135,H:H,I:I)-D135),0)</f>
+        <v>1648</v>
       </c>
       <c r="F135">
-        <f t="shared" si="17"/>
-        <v>-3</v>
+        <f>E135-D135</f>
+        <v>41</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>39</v>
-      </c>
-      <c r="B136" t="s">
-        <v>156</v>
+        <v>105</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D136">
-        <v>3298</v>
+        <v>1826</v>
       </c>
       <c r="E136">
-        <f t="shared" si="18"/>
-        <v>3286</v>
+        <f>ROUND(D136+$K$2*(_xlfn.XLOOKUP(C136,H:H,I:I)-D136),0)</f>
+        <v>1795</v>
       </c>
       <c r="F136">
-        <f t="shared" si="17"/>
-        <v>-12</v>
+        <f>E136-D136</f>
+        <v>-31</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>71</v>
-      </c>
-      <c r="B137" t="s">
-        <v>157</v>
+        <v>118</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D137">
-        <v>2676</v>
+        <v>1491</v>
       </c>
       <c r="E137">
-        <f t="shared" si="18"/>
-        <v>2608</v>
+        <f>ROUND(D137+$K$2*(_xlfn.XLOOKUP(C137,H:H,I:I)-D137),0)</f>
+        <v>1570</v>
       </c>
       <c r="F137">
-        <f t="shared" si="17"/>
-        <v>-68</v>
+        <f>E137-D137</f>
+        <v>79</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>123</v>
-      </c>
-      <c r="B138" t="s">
-        <v>158</v>
+        <v>108</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D138">
-        <v>1302</v>
+        <v>1775</v>
       </c>
       <c r="E138">
-        <f t="shared" si="18"/>
-        <v>1370</v>
+        <f>ROUND(D138+$K$2*(_xlfn.XLOOKUP(C138,H:H,I:I)-D138),0)</f>
+        <v>1760</v>
       </c>
       <c r="F138">
-        <f t="shared" si="17"/>
-        <v>68</v>
+        <f>E138-D138</f>
+        <v>-15</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>55</v>
-      </c>
-      <c r="B139" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D139">
-        <v>3002</v>
+        <v>1667</v>
       </c>
       <c r="E139">
-        <f t="shared" si="18"/>
-        <v>2984</v>
+        <f>ROUND(D139+$K$2*(_xlfn.XLOOKUP(C139,H:H,I:I)-D139),0)</f>
+        <v>1688</v>
       </c>
       <c r="F139">
-        <f t="shared" si="17"/>
-        <v>-18</v>
+        <f>E139-D139</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>119</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D140">
+        <v>1449</v>
+      </c>
+      <c r="E140">
+        <f>ROUND(D140+$K$2*(_xlfn.XLOOKUP(C140,H:H,I:I)-D140),0)</f>
+        <v>1519</v>
+      </c>
+      <c r="F140">
+        <f>E140-D140</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>120</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D141">
+        <v>1366</v>
+      </c>
+      <c r="E141">
+        <f>ROUND(D141+$K$2*(_xlfn.XLOOKUP(C141,H:H,I:I)-D141),0)</f>
+        <v>1464</v>
+      </c>
+      <c r="F141">
+        <f>E141-D141</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>101</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D142">
+        <v>1850</v>
+      </c>
+      <c r="E142">
+        <f>ROUND(D142+$K$2*(_xlfn.XLOOKUP(C142,H:H,I:I)-D142),0)</f>
+        <v>1788</v>
+      </c>
+      <c r="F142">
+        <f>E142-D142</f>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>116</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D143">
+        <v>1548</v>
+      </c>
+      <c r="E143">
+        <f>ROUND(D143+$K$2*(_xlfn.XLOOKUP(C143,H:H,I:I)-D143),0)</f>
+        <v>1586</v>
+      </c>
+      <c r="F143">
+        <f>E143-D143</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>104</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D144">
+        <v>1823</v>
+      </c>
+      <c r="E144">
+        <f>ROUND(D144+$K$2*(_xlfn.XLOOKUP(C144,H:H,I:I)-D144),0)</f>
+        <v>1770</v>
+      </c>
+      <c r="F144">
+        <f>E144-D144</f>
+        <v>-53</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>115</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D145">
+        <v>1552</v>
+      </c>
+      <c r="E145">
+        <f>ROUND(D145+$K$2*(_xlfn.XLOOKUP(C145,H:H,I:I)-D145),0)</f>
+        <v>1588</v>
+      </c>
+      <c r="F145">
+        <f>E145-D145</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>114</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D146">
+        <v>1605</v>
+      </c>
+      <c r="E146">
+        <f>ROUND(D146+$K$2*(_xlfn.XLOOKUP(C146,H:H,I:I)-D146),0)</f>
+        <v>1624</v>
+      </c>
+      <c r="F146">
+        <f>E146-D146</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>107</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D147">
+        <v>1778</v>
+      </c>
+      <c r="E147">
+        <f>ROUND(D147+$K$2*(_xlfn.XLOOKUP(C147,H:H,I:I)-D147),0)</f>
+        <v>1740</v>
+      </c>
+      <c r="F147">
+        <f>E147-D147</f>
+        <v>-38</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B148" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D148">
+        <v>1985</v>
+      </c>
+      <c r="E148">
+        <f>ROUND(D148+$K$2*(_xlfn.XLOOKUP(C148,H:H,I:I)-D148),0)</f>
+        <v>1878</v>
+      </c>
+      <c r="F148">
+        <f>E148-D148</f>
+        <v>-107</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B149" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D149">
+        <v>1529</v>
+      </c>
+      <c r="E149">
+        <f>ROUND(D149+$K$2*(_xlfn.XLOOKUP(C149,H:H,I:I)-D149),0)</f>
+        <v>1596</v>
+      </c>
+      <c r="F149">
+        <f>E149-D149</f>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B150" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D150">
+        <v>1917</v>
+      </c>
+      <c r="E150">
+        <f>ROUND(D150+$K$2*(_xlfn.XLOOKUP(C150,H:H,I:I)-D150),0)</f>
+        <v>1856</v>
+      </c>
+      <c r="F150">
+        <f>E150-D150</f>
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B151" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D151">
+        <v>2021</v>
+      </c>
+      <c r="E151">
+        <f>ROUND(D151+$K$2*(_xlfn.XLOOKUP(C151,H:H,I:I)-D151),0)</f>
+        <v>1925</v>
+      </c>
+      <c r="F151">
+        <f>E151-D151</f>
+        <v>-96</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>112</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152">
+        <v>1642</v>
+      </c>
+      <c r="E152">
+        <f>ROUND(D152+$K$2*(_xlfn.XLOOKUP(C152,H:H,I:I)-D152),0)</f>
+        <v>1568</v>
+      </c>
+      <c r="F152">
+        <f>E152-D152</f>
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>127</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153">
+        <v>1211</v>
+      </c>
+      <c r="E153">
+        <f>ROUND(D153+$K$2*(_xlfn.XLOOKUP(C153,H:H,I:I)-D153),0)</f>
+        <v>1279</v>
+      </c>
+      <c r="F153">
+        <f>E153-D153</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>117</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D154">
+        <v>1516</v>
+      </c>
+      <c r="E154">
+        <f>ROUND(D154+$K$2*(_xlfn.XLOOKUP(C154,H:H,I:I)-D154),0)</f>
+        <v>1484</v>
+      </c>
+      <c r="F154">
+        <f>E154-D154</f>
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>123</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155">
+        <v>1302</v>
+      </c>
+      <c r="E155">
+        <f>ROUND(D155+$K$2*(_xlfn.XLOOKUP(C155,H:H,I:I)-D155),0)</f>
+        <v>1340</v>
+      </c>
+      <c r="F155">
+        <f>E155-D155</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B156" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D156" s="4">
+        <v>1175</v>
+      </c>
+      <c r="E156" s="4">
+        <f>ROUND(D156+$K$2*(_xlfn.XLOOKUP(C156,H:H,I:I)-D156),0)</f>
+        <v>1175</v>
+      </c>
+      <c r="F156">
+        <f>E156-D156</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>121</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D157">
+        <v>1361</v>
+      </c>
+      <c r="E157">
+        <f>ROUND(D157+$K$2*(_xlfn.XLOOKUP(C157,H:H,I:I)-D157),0)</f>
+        <v>1300</v>
+      </c>
+      <c r="F157">
+        <f>E157-D157</f>
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>133</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D158">
+        <v>989</v>
+      </c>
+      <c r="E158">
+        <f>ROUND(D158+$K$2*(_xlfn.XLOOKUP(C158,H:H,I:I)-D158),0)</f>
+        <v>1050</v>
+      </c>
+      <c r="F158">
+        <f>E158-D158</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>125</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D159">
+        <v>1240</v>
+      </c>
+      <c r="E159">
+        <f>ROUND(D159+$K$2*(_xlfn.XLOOKUP(C159,H:H,I:I)-D159),0)</f>
+        <v>1219</v>
+      </c>
+      <c r="F159">
+        <f>E159-D159</f>
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>122</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D160">
+        <v>1348</v>
+      </c>
+      <c r="E160">
+        <f>ROUND(D160+$K$2*(_xlfn.XLOOKUP(C160,H:H,I:I)-D160),0)</f>
+        <v>1291</v>
+      </c>
+      <c r="F160">
+        <f>E160-D160</f>
+        <v>-57</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>129</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D161">
+        <v>1095</v>
+      </c>
+      <c r="E161">
+        <f>ROUND(D161+$K$2*(_xlfn.XLOOKUP(C161,H:H,I:I)-D161),0)</f>
+        <v>1121</v>
+      </c>
+      <c r="F161">
+        <f>E161-D161</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>134</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D162">
+        <v>986</v>
+      </c>
+      <c r="E162">
+        <f>ROUND(D162+$K$2*(_xlfn.XLOOKUP(C162,H:H,I:I)-D162),0)</f>
+        <v>1048</v>
+      </c>
+      <c r="F162">
+        <f>E162-D162</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>128</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D163">
+        <v>1207</v>
+      </c>
+      <c r="E163">
+        <f>ROUND(D163+$K$2*(_xlfn.XLOOKUP(C163,H:H,I:I)-D163),0)</f>
+        <v>1196</v>
+      </c>
+      <c r="F163">
+        <f>E163-D163</f>
+        <v>-11</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D139">
-    <sortCondition ref="B2:B139"/>
+  <autoFilter ref="A1:F163" xr:uid="{7D935EE6-5B9C-4F74-9C70-F47CE547CAED}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F163">
+      <sortCondition ref="C1:C163"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J63:K172">
+    <sortCondition ref="K63:K172"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>